--- a/OR_year1_awardees.xlsx
+++ b/OR_year1_awardees.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="724">
   <si>
     <t xml:space="preserve">README</t>
   </si>
@@ -1846,15 +1846,18 @@
     <t xml:space="preserve">2026-04-10</t>
   </si>
   <si>
+    <t xml:space="preserve">§6.2 MULTI_RECIPIENT_FIELD: OHA publishes ONE figure against several named organisations in a single awardee field, so the recipient list is unresolved. The amount is never divided (§6.2) and no organisation in the field is imputed to have received it (§0.3) -- including any hospital named in it, which is what this override exists to prevent. PASS_THROUGH_UNRESOLVED + Unclear, in NEITHER hospital bucket, routed to a reviewer. THIS SUPERSEDES THE NAME-BASED DETERMINATION BELOW, which was written from the field as if it named one recipient. [Superseded machine basis, kept for audit: Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columbia Gorge Health Council</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connected Care for Older Adults</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
   </si>
   <si>
-    <t xml:space="preserve">Columbia Gorge Health Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connected Care for Older Adults</t>
-  </si>
-  <si>
     <t xml:space="preserve">Family Connects Oregon</t>
   </si>
   <si>
@@ -1888,7 +1891,7 @@
     <t xml:space="preserve">PATTERN</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount.</t>
+    <t xml:space="preserve">§6.2 MULTI_RECIPIENT_FIELD: OHA publishes ONE figure against several named organisations in a single awardee field, so the recipient list is unresolved. The amount is never divided (§6.2) and no organisation in the field is imputed to have received it (§0.3) -- including any hospital named in it, which is what this override exists to prevent. PASS_THROUGH_UNRESOLVED + Unclear, in NEITHER hospital bucket, routed to a reviewer. THIS SUPERSEDES THE NAME-BASED DETERMINATION BELOW, which was written from the field as if it named one recipient. [Superseded machine basis, kept for audit: Recipient name rule: name states a hospital. §10.2 DIRECT: the named recipient is a hospital or hospital system and the state's award document names both the recipient and the amount.]</t>
   </si>
   <si>
     <t xml:space="preserve">Oregon ECHO Network (ORPRN)</t>
@@ -2114,6 +2117,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tribal Initiative (set-aside for the Nine Federally Recognized Tribes of Oregon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§0.3 AGGREGATE ROW, NOT A RECIPIENT: OHA publishes this pool as a total and names no member of it, so `recipient_type` is NOT_YET_NAMED, `amount` is deliberately empty and the pool total is carried in `pool_amount`. PASS_THROUGH_UNRESOLVED + Unclear because a count is not a list and nothing may be imputed to the unnamed. This row enters NEITHER bucket of rhtp_hospital_dollar_partition(). The classifier's name-based sentence is DISCARDED rather than kept behind this one, unlike the multi-recipient rows below: it read "Recipient is named but the source does not state its organisational form" against an awardee of "Not identified in the source", which is not a superseded determination but an artefact of running a name rule on a row that has no name.</t>
   </si>
   <si>
     <t xml:space="preserve">AGGREGATE ROW, NOT A RECIPIENT. $5,000,000 to 33 local public health authorities; OHA names none. `amount` is deliberately empty.</t>
@@ -27722,7 +27728,7 @@
         <v>353</v>
       </c>
       <c r="AP240" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="241">
@@ -27733,7 +27739,7 @@
         <v>240</v>
       </c>
       <c r="C241" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D241" t="n">
         <v>631000</v>
@@ -27791,7 +27797,7 @@
         <v>605</v>
       </c>
       <c r="Y241" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Z241" t="n">
         <v>631000</v>
@@ -27805,7 +27811,7 @@
       <c r="AG241"/>
       <c r="AH241"/>
       <c r="AI241" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AJ241" t="s">
         <v>148</v>
@@ -27824,7 +27830,7 @@
         <v>353</v>
       </c>
       <c r="AP241" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="242">
@@ -27835,7 +27841,7 @@
         <v>241</v>
       </c>
       <c r="C242" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D242" t="n">
         <v>502000</v>
@@ -27890,10 +27896,10 @@
         <v>604</v>
       </c>
       <c r="X242" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y242" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="Z242" t="n">
         <v>502000</v>
@@ -27907,7 +27913,7 @@
       <c r="AG242"/>
       <c r="AH242"/>
       <c r="AI242" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AJ242" t="s">
         <v>148</v>
@@ -27926,7 +27932,7 @@
         <v>353</v>
       </c>
       <c r="AP242" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="243">
@@ -27937,7 +27943,7 @@
         <v>242</v>
       </c>
       <c r="C243" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D243" t="n">
         <v>186000</v>
@@ -27986,16 +27992,16 @@
         <v>350</v>
       </c>
       <c r="V243" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="W243" t="s">
         <v>604</v>
       </c>
       <c r="X243" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y243" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Z243" t="n">
         <v>186000</v>
@@ -28025,10 +28031,10 @@
         <v>608</v>
       </c>
       <c r="AO243" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP243" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="244">
@@ -28039,7 +28045,7 @@
         <v>243</v>
       </c>
       <c r="C244" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D244" t="n">
         <v>159000</v>
@@ -28094,10 +28100,10 @@
         <v>604</v>
       </c>
       <c r="X244" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y244" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="Z244" t="n">
         <v>159000</v>
@@ -28130,7 +28136,7 @@
         <v>353</v>
       </c>
       <c r="AP244" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="245">
@@ -28141,7 +28147,7 @@
         <v>244</v>
       </c>
       <c r="C245" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D245" t="n">
         <v>398000</v>
@@ -28196,10 +28202,10 @@
         <v>604</v>
       </c>
       <c r="X245" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y245" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="Z245" t="n">
         <v>398000</v>
@@ -28229,10 +28235,10 @@
         <v>608</v>
       </c>
       <c r="AO245" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP245" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="246">
@@ -28243,7 +28249,7 @@
         <v>245</v>
       </c>
       <c r="C246" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D246" t="n">
         <v>610000</v>
@@ -28298,10 +28304,10 @@
         <v>604</v>
       </c>
       <c r="X246" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y246" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Z246" t="n">
         <v>610000</v>
@@ -28334,7 +28340,7 @@
         <v>353</v>
       </c>
       <c r="AP246" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="247">
@@ -28345,7 +28351,7 @@
         <v>246</v>
       </c>
       <c r="C247" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D247" t="n">
         <v>363000</v>
@@ -28403,7 +28409,7 @@
         <v>605</v>
       </c>
       <c r="Y247" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Z247" t="n">
         <v>363000</v>
@@ -28447,7 +28453,7 @@
         <v>247</v>
       </c>
       <c r="C248" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D248"/>
       <c r="E248" t="s">
@@ -28494,7 +28500,7 @@
         <v>350</v>
       </c>
       <c r="V248" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="W248" t="s">
         <v>604</v>
@@ -28503,7 +28509,7 @@
         <v>605</v>
       </c>
       <c r="Y248" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="Z248" t="n">
         <v>403000</v>
@@ -28538,7 +28544,7 @@
         <v>353</v>
       </c>
       <c r="AP248" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="249">
@@ -28549,7 +28555,7 @@
         <v>248</v>
       </c>
       <c r="C249" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D249" t="n">
         <v>107000</v>
@@ -28607,7 +28613,7 @@
         <v>605</v>
       </c>
       <c r="Y249" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Z249" t="n">
         <v>107000</v>
@@ -28637,10 +28643,10 @@
         <v>608</v>
       </c>
       <c r="AO249" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP249" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="250">
@@ -28651,7 +28657,7 @@
         <v>249</v>
       </c>
       <c r="C250" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D250"/>
       <c r="E250" t="s">
@@ -28698,7 +28704,7 @@
         <v>350</v>
       </c>
       <c r="V250" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="W250" t="s">
         <v>604</v>
@@ -28707,7 +28713,7 @@
         <v>605</v>
       </c>
       <c r="Y250" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Z250" t="n">
         <v>102000</v>
@@ -28742,7 +28748,7 @@
         <v>353</v>
       </c>
       <c r="AP250" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="251">
@@ -28753,7 +28759,7 @@
         <v>250</v>
       </c>
       <c r="C251" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D251" t="n">
         <v>515051</v>
@@ -28765,7 +28771,7 @@
         <v>86</v>
       </c>
       <c r="G251" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H251" t="s">
         <v>84</v>
@@ -28805,13 +28811,13 @@
         <v>351</v>
       </c>
       <c r="W251" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X251" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y251" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="Z251" t="n">
         <v>515051</v>
@@ -28844,7 +28850,7 @@
         <v>353</v>
       </c>
       <c r="AP251" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="252">
@@ -28855,7 +28861,7 @@
         <v>251</v>
       </c>
       <c r="C252" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D252" t="n">
         <v>412635</v>
@@ -28867,7 +28873,7 @@
         <v>86</v>
       </c>
       <c r="G252" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H252" t="s">
         <v>84</v>
@@ -28907,13 +28913,13 @@
         <v>351</v>
       </c>
       <c r="W252" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X252" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y252" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="Z252" t="n">
         <v>412635</v>
@@ -28946,7 +28952,7 @@
         <v>353</v>
       </c>
       <c r="AP252" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="253">
@@ -28957,7 +28963,7 @@
         <v>252</v>
       </c>
       <c r="C253" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D253" t="n">
         <v>288104</v>
@@ -28969,7 +28975,7 @@
         <v>86</v>
       </c>
       <c r="G253" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H253" t="s">
         <v>84</v>
@@ -29009,13 +29015,13 @@
         <v>351</v>
       </c>
       <c r="W253" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X253" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y253" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Z253" t="n">
         <v>288104</v>
@@ -29048,7 +29054,7 @@
         <v>353</v>
       </c>
       <c r="AP253" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="254">
@@ -29059,7 +29065,7 @@
         <v>253</v>
       </c>
       <c r="C254" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D254" t="n">
         <v>80765</v>
@@ -29071,7 +29077,7 @@
         <v>86</v>
       </c>
       <c r="G254" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H254" t="s">
         <v>84</v>
@@ -29108,16 +29114,16 @@
         <v>350</v>
       </c>
       <c r="V254" t="s">
+        <v>651</v>
+      </c>
+      <c r="W254" t="s">
+        <v>643</v>
+      </c>
+      <c r="X254" t="s">
+        <v>618</v>
+      </c>
+      <c r="Y254" t="s">
         <v>650</v>
-      </c>
-      <c r="W254" t="s">
-        <v>642</v>
-      </c>
-      <c r="X254" t="s">
-        <v>617</v>
-      </c>
-      <c r="Y254" t="s">
-        <v>649</v>
       </c>
       <c r="Z254" t="n">
         <v>80765</v>
@@ -29150,7 +29156,7 @@
         <v>353</v>
       </c>
       <c r="AP254" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="255">
@@ -29161,19 +29167,19 @@
         <v>254</v>
       </c>
       <c r="C255" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D255" t="n">
         <v>249800</v>
       </c>
       <c r="E255" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F255" t="s">
         <v>86</v>
       </c>
       <c r="G255" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H255" t="s">
         <v>84</v>
@@ -29213,13 +29219,13 @@
         <v>95</v>
       </c>
       <c r="W255" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X255" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y255" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Z255" t="n">
         <v>249800</v>
@@ -29249,10 +29255,10 @@
         <v>259</v>
       </c>
       <c r="AO255" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP255" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="256">
@@ -29263,7 +29269,7 @@
         <v>255</v>
       </c>
       <c r="C256" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D256" t="n">
         <v>138902</v>
@@ -29275,7 +29281,7 @@
         <v>86</v>
       </c>
       <c r="G256" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H256" t="s">
         <v>84</v>
@@ -29312,16 +29318,16 @@
         <v>350</v>
       </c>
       <c r="V256" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="W256" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X256" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y256" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="Z256" t="n">
         <v>138902</v>
@@ -29354,7 +29360,7 @@
         <v>353</v>
       </c>
       <c r="AP256" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="257">
@@ -29365,7 +29371,7 @@
         <v>256</v>
       </c>
       <c r="C257" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D257" t="n">
         <v>208472</v>
@@ -29377,7 +29383,7 @@
         <v>86</v>
       </c>
       <c r="G257" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H257" t="s">
         <v>84</v>
@@ -29417,13 +29423,13 @@
         <v>351</v>
       </c>
       <c r="W257" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X257" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y257" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Z257" t="n">
         <v>208472</v>
@@ -29456,7 +29462,7 @@
         <v>353</v>
       </c>
       <c r="AP257" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="258">
@@ -29467,7 +29473,7 @@
         <v>257</v>
       </c>
       <c r="C258" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D258" t="n">
         <v>1096657</v>
@@ -29479,7 +29485,7 @@
         <v>86</v>
       </c>
       <c r="G258" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H258" t="s">
         <v>84</v>
@@ -29519,13 +29525,13 @@
         <v>351</v>
       </c>
       <c r="W258" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X258" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y258" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Z258" t="n">
         <v>1096657</v>
@@ -29558,7 +29564,7 @@
         <v>353</v>
       </c>
       <c r="AP258" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="259">
@@ -29569,7 +29575,7 @@
         <v>258</v>
       </c>
       <c r="C259" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D259" t="n">
         <v>235581</v>
@@ -29581,7 +29587,7 @@
         <v>599</v>
       </c>
       <c r="G259" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H259" t="s">
         <v>84</v>
@@ -29621,13 +29627,13 @@
         <v>603</v>
       </c>
       <c r="W259" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X259" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y259" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="Z259" t="n">
         <v>235581</v>
@@ -29671,19 +29677,19 @@
         <v>259</v>
       </c>
       <c r="C260" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D260" t="n">
         <v>356333</v>
       </c>
       <c r="E260" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F260" t="s">
         <v>86</v>
       </c>
       <c r="G260" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H260" t="s">
         <v>84</v>
@@ -29723,13 +29729,13 @@
         <v>95</v>
       </c>
       <c r="W260" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X260" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y260" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="Z260" t="n">
         <v>356333</v>
@@ -29759,10 +29765,10 @@
         <v>259</v>
       </c>
       <c r="AO260" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP260" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="261">
@@ -29773,7 +29779,7 @@
         <v>260</v>
       </c>
       <c r="C261" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D261" t="n">
         <v>783516</v>
@@ -29785,7 +29791,7 @@
         <v>86</v>
       </c>
       <c r="G261" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H261" t="s">
         <v>84</v>
@@ -29825,13 +29831,13 @@
         <v>351</v>
       </c>
       <c r="W261" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X261" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y261" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Z261" t="n">
         <v>783516</v>
@@ -29864,7 +29870,7 @@
         <v>353</v>
       </c>
       <c r="AP261" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="262">
@@ -29875,7 +29881,7 @@
         <v>261</v>
       </c>
       <c r="C262" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D262" t="n">
         <v>320281</v>
@@ -29887,7 +29893,7 @@
         <v>86</v>
       </c>
       <c r="G262" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H262" t="s">
         <v>84</v>
@@ -29927,13 +29933,13 @@
         <v>351</v>
       </c>
       <c r="W262" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X262" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y262" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Z262" t="n">
         <v>320281</v>
@@ -29966,7 +29972,7 @@
         <v>353</v>
       </c>
       <c r="AP262" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="263">
@@ -29977,7 +29983,7 @@
         <v>262</v>
       </c>
       <c r="C263" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D263" t="n">
         <v>77000</v>
@@ -29989,7 +29995,7 @@
         <v>86</v>
       </c>
       <c r="G263" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H263" t="s">
         <v>84</v>
@@ -30029,13 +30035,13 @@
         <v>351</v>
       </c>
       <c r="W263" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X263" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y263" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="Z263" t="n">
         <v>77000</v>
@@ -30068,7 +30074,7 @@
         <v>353</v>
       </c>
       <c r="AP263" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="264">
@@ -30079,19 +30085,19 @@
         <v>263</v>
       </c>
       <c r="C264" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D264" t="n">
         <v>1012479</v>
       </c>
       <c r="E264" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F264" t="s">
         <v>86</v>
       </c>
       <c r="G264" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H264" t="s">
         <v>84</v>
@@ -30131,13 +30137,13 @@
         <v>95</v>
       </c>
       <c r="W264" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X264" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y264" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="Z264" t="n">
         <v>1012479</v>
@@ -30167,10 +30173,10 @@
         <v>259</v>
       </c>
       <c r="AO264" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP264" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="265">
@@ -30181,7 +30187,7 @@
         <v>264</v>
       </c>
       <c r="C265" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D265" t="n">
         <v>1000000</v>
@@ -30193,7 +30199,7 @@
         <v>86</v>
       </c>
       <c r="G265" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H265" t="s">
         <v>84</v>
@@ -30233,13 +30239,13 @@
         <v>351</v>
       </c>
       <c r="W265" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X265" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y265" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="Z265" t="n">
         <v>1000000</v>
@@ -30272,7 +30278,7 @@
         <v>353</v>
       </c>
       <c r="AP265" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="266">
@@ -30283,19 +30289,19 @@
         <v>265</v>
       </c>
       <c r="C266" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D266" t="n">
         <v>1400000</v>
       </c>
       <c r="E266" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F266" t="s">
         <v>86</v>
       </c>
       <c r="G266" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H266" t="s">
         <v>84</v>
@@ -30335,13 +30341,13 @@
         <v>95</v>
       </c>
       <c r="W266" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X266" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y266" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Z266" t="n">
         <v>1400000</v>
@@ -30371,10 +30377,10 @@
         <v>259</v>
       </c>
       <c r="AO266" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP266" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="267">
@@ -30385,7 +30391,7 @@
         <v>266</v>
       </c>
       <c r="C267" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D267" t="n">
         <v>255447</v>
@@ -30397,7 +30403,7 @@
         <v>86</v>
       </c>
       <c r="G267" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H267" t="s">
         <v>84</v>
@@ -30437,13 +30443,13 @@
         <v>351</v>
       </c>
       <c r="W267" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X267" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y267" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Z267" t="n">
         <v>255447</v>
@@ -30476,7 +30482,7 @@
         <v>353</v>
       </c>
       <c r="AP267" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="268">
@@ -30487,7 +30493,7 @@
         <v>267</v>
       </c>
       <c r="C268" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D268" t="n">
         <v>79615</v>
@@ -30499,7 +30505,7 @@
         <v>86</v>
       </c>
       <c r="G268" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H268" t="s">
         <v>84</v>
@@ -30539,13 +30545,13 @@
         <v>351</v>
       </c>
       <c r="W268" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X268" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y268" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="Z268" t="n">
         <v>79615</v>
@@ -30578,7 +30584,7 @@
         <v>353</v>
       </c>
       <c r="AP268" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="269">
@@ -30589,7 +30595,7 @@
         <v>268</v>
       </c>
       <c r="C269" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D269" t="n">
         <v>254334</v>
@@ -30601,7 +30607,7 @@
         <v>86</v>
       </c>
       <c r="G269" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H269" t="s">
         <v>84</v>
@@ -30638,16 +30644,16 @@
         <v>350</v>
       </c>
       <c r="V269" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="W269" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X269" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y269" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="Z269" t="n">
         <v>254334</v>
@@ -30680,7 +30686,7 @@
         <v>353</v>
       </c>
       <c r="AP269" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="270">
@@ -30691,7 +30697,7 @@
         <v>269</v>
       </c>
       <c r="C270" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D270" t="n">
         <v>368063</v>
@@ -30703,7 +30709,7 @@
         <v>86</v>
       </c>
       <c r="G270" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H270" t="s">
         <v>84</v>
@@ -30743,13 +30749,13 @@
         <v>351</v>
       </c>
       <c r="W270" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X270" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y270" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="Z270" t="n">
         <v>368063</v>
@@ -30782,7 +30788,7 @@
         <v>353</v>
       </c>
       <c r="AP270" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="271">
@@ -30793,7 +30799,7 @@
         <v>270</v>
       </c>
       <c r="C271" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D271"/>
       <c r="E271" t="s">
@@ -30803,7 +30809,7 @@
         <v>86</v>
       </c>
       <c r="G271" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H271" t="s">
         <v>84</v>
@@ -30840,16 +30846,16 @@
         <v>350</v>
       </c>
       <c r="V271" t="s">
+        <v>683</v>
+      </c>
+      <c r="W271" t="s">
+        <v>643</v>
+      </c>
+      <c r="X271" t="s">
+        <v>644</v>
+      </c>
+      <c r="Y271" t="s">
         <v>682</v>
-      </c>
-      <c r="W271" t="s">
-        <v>642</v>
-      </c>
-      <c r="X271" t="s">
-        <v>643</v>
-      </c>
-      <c r="Y271" t="s">
-        <v>681</v>
       </c>
       <c r="Z271"/>
       <c r="AA271"/>
@@ -30880,7 +30886,7 @@
         <v>353</v>
       </c>
       <c r="AP271" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="272">
@@ -30891,7 +30897,7 @@
         <v>271</v>
       </c>
       <c r="C272" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D272"/>
       <c r="E272" t="s">
@@ -30901,7 +30907,7 @@
         <v>86</v>
       </c>
       <c r="G272" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H272" t="s">
         <v>84</v>
@@ -30938,16 +30944,16 @@
         <v>350</v>
       </c>
       <c r="V272" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="W272" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X272" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y272" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="Z272"/>
       <c r="AA272"/>
@@ -30978,7 +30984,7 @@
         <v>353</v>
       </c>
       <c r="AP272" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="273">
@@ -30989,7 +30995,7 @@
         <v>272</v>
       </c>
       <c r="C273" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D273" t="n">
         <v>146986</v>
@@ -31001,7 +31007,7 @@
         <v>86</v>
       </c>
       <c r="G273" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H273" t="s">
         <v>84</v>
@@ -31041,13 +31047,13 @@
         <v>351</v>
       </c>
       <c r="W273" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X273" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y273" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="Z273" t="n">
         <v>146986</v>
@@ -31080,7 +31086,7 @@
         <v>353</v>
       </c>
       <c r="AP273" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="274">
@@ -31091,7 +31097,7 @@
         <v>273</v>
       </c>
       <c r="C274" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D274" t="n">
         <v>362760</v>
@@ -31103,7 +31109,7 @@
         <v>86</v>
       </c>
       <c r="G274" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H274" t="s">
         <v>84</v>
@@ -31143,13 +31149,13 @@
         <v>351</v>
       </c>
       <c r="W274" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X274" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y274" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Z274" t="n">
         <v>362760</v>
@@ -31182,7 +31188,7 @@
         <v>353</v>
       </c>
       <c r="AP274" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="275">
@@ -31193,7 +31199,7 @@
         <v>274</v>
       </c>
       <c r="C275" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D275" t="n">
         <v>358171</v>
@@ -31205,7 +31211,7 @@
         <v>86</v>
       </c>
       <c r="G275" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H275" t="s">
         <v>84</v>
@@ -31242,16 +31248,16 @@
         <v>350</v>
       </c>
       <c r="V275" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="W275" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X275" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y275" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Z275" t="n">
         <v>358171</v>
@@ -31284,7 +31290,7 @@
         <v>353</v>
       </c>
       <c r="AP275" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="276">
@@ -31295,7 +31301,7 @@
         <v>275</v>
       </c>
       <c r="C276" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D276" t="n">
         <v>328031</v>
@@ -31307,7 +31313,7 @@
         <v>86</v>
       </c>
       <c r="G276" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H276" t="s">
         <v>84</v>
@@ -31347,13 +31353,13 @@
         <v>351</v>
       </c>
       <c r="W276" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X276" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y276" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="Z276" t="n">
         <v>328031</v>
@@ -31386,7 +31392,7 @@
         <v>353</v>
       </c>
       <c r="AP276" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="277">
@@ -31409,7 +31415,7 @@
         <v>86</v>
       </c>
       <c r="G277" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H277" t="s">
         <v>84</v>
@@ -31449,13 +31455,13 @@
         <v>351</v>
       </c>
       <c r="W277" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X277" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y277" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Z277" t="n">
         <v>965661</v>
@@ -31488,7 +31494,7 @@
         <v>353</v>
       </c>
       <c r="AP277" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="278">
@@ -31499,17 +31505,17 @@
         <v>277</v>
       </c>
       <c r="C278" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D278"/>
       <c r="E278" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F278" t="s">
         <v>599</v>
       </c>
       <c r="G278" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H278" t="s">
         <v>86</v>
@@ -31521,13 +31527,13 @@
         <v>87</v>
       </c>
       <c r="K278" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L278" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M278" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N278" t="s">
         <v>91</v>
@@ -31546,13 +31552,13 @@
         <v>350</v>
       </c>
       <c r="V278" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="W278" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="X278" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Y278"/>
       <c r="Z278"/>
@@ -31588,7 +31594,7 @@
         <v>353</v>
       </c>
       <c r="AP278" t="s">
-        <v>609</v>
+        <v>700</v>
       </c>
     </row>
     <row r="279">
@@ -31599,17 +31605,17 @@
         <v>278</v>
       </c>
       <c r="C279" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D279"/>
       <c r="E279" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F279" t="s">
         <v>599</v>
       </c>
       <c r="G279" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="H279" t="s">
         <v>86</v>
@@ -31621,13 +31627,13 @@
         <v>87</v>
       </c>
       <c r="K279" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L279" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M279" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N279" t="s">
         <v>91</v>
@@ -31646,13 +31652,13 @@
         <v>350</v>
       </c>
       <c r="V279" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="W279" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="X279" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="Y279"/>
       <c r="Z279"/>
@@ -31688,7 +31694,7 @@
         <v>353</v>
       </c>
       <c r="AP279" t="s">
-        <v>609</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -31718,22 +31724,22 @@
         <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="E1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="F1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="2">
@@ -31784,7 +31790,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B4" t="n">
         <v>27</v>
@@ -31830,7 +31836,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -31876,7 +31882,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -31909,17 +31915,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="15">
@@ -31929,22 +31935,22 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="20">
@@ -31954,12 +31960,12 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="23">
@@ -31969,7 +31975,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="25">
@@ -31982,13 +31988,13 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C26" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D26" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="27">
